--- a/Plannification/Planning miniProjet.xlsx
+++ b/Plannification/Planning miniProjet.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\matisse.begaud\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stfelixlasalle-my.sharepoint.com/personal/julian_chedotal_stfelixlasalle_fr/Documents/Documents/GitHub/mini_projet2/mini_projet2/Plannification/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D6FB2EA4-EEBF-4953-9A47-F4C5A052C07B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="8_{D6FB2EA4-EEBF-4953-9A47-F4C5A052C07B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D8A22FC-4CB0-49BE-BEA6-69B46161132D}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0BF01B35-82F2-4CD7-817C-7D55880151BB}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>12 heure</t>
   </si>
@@ -63,6 +63,9 @@
   </si>
   <si>
     <t>regarder les extensions VS Code</t>
+  </si>
+  <si>
+    <t>Cookie de connexion au chat générale</t>
   </si>
 </sst>
 </file>
@@ -85,7 +88,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -122,6 +125,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -135,20 +144,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -156,11 +168,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -177,10 +189,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -509,112 +517,114 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="5"/>
+      <c r="E1" s="9"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="3"/>
+      <c r="A2" s="6"/>
       <c r="B2"/>
       <c r="C2"/>
       <c r="D2"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="3"/>
+      <c r="A3" s="6"/>
       <c r="B3"/>
       <c r="C3"/>
       <c r="D3"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="3"/>
+      <c r="A4" s="6"/>
       <c r="B4"/>
       <c r="C4"/>
       <c r="D4"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="3"/>
+      <c r="A5" s="6"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="3"/>
+      <c r="A7" s="6"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="3"/>
+      <c r="A8" s="6"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="3"/>
+      <c r="A9" s="6"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="3"/>
+      <c r="A10" s="6"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G11" s="10"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="10"/>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="3"/>
+      <c r="A12" s="6"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="3"/>
+      <c r="A13" s="6"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="3"/>
+      <c r="A14" s="6"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="3"/>
+      <c r="A15" s="6"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="8"/>
-      <c r="J16" s="8"/>
-      <c r="K16" s="8"/>
-      <c r="L16" s="8"/>
-      <c r="M16" s="8"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="5"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="B16:M16"/>
     <mergeCell ref="A1:A5"/>
     <mergeCell ref="A6:A10"/>
@@ -622,26 +632,28 @@
     <mergeCell ref="B6:E6"/>
     <mergeCell ref="B11:E11"/>
     <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F11:I11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="25b9d25b-f3e3-4424-a4f0-1b70bb014b4c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="25b9d25b-f3e3-4424-a4f0-1b70bb014b4c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -827,6 +839,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5531CBBA-C22C-419D-9C9F-1BADD5578B4A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2E1627CE-88CC-44E6-B4B2-E6F7C128AD9F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
@@ -838,14 +858,6 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5531CBBA-C22C-419D-9C9F-1BADD5578B4A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Plannification/Planning miniProjet.xlsx
+++ b/Plannification/Planning miniProjet.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stfelixlasalle-my.sharepoint.com/personal/julian_chedotal_stfelixlasalle_fr/Documents/Documents/GitHub/mini_projet2/mini_projet2/Plannification/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\matisse.begaud\Documents\GitHub\mini_projet2\Plannification\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="8_{D6FB2EA4-EEBF-4953-9A47-F4C5A052C07B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D8A22FC-4CB0-49BE-BEA6-69B46161132D}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FDB723D-C4E9-4112-993E-2B9D3F28E948}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0BF01B35-82F2-4CD7-817C-7D55880151BB}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>12 heure</t>
   </si>
@@ -66,13 +66,19 @@
   </si>
   <si>
     <t>Cookie de connexion au chat générale</t>
+  </si>
+  <si>
+    <t>travailler sur le chat générale</t>
+  </si>
+  <si>
+    <t>lié mail par compte</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -87,8 +93,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -131,6 +143,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.89999084444715716"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -144,7 +162,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -171,8 +189,14 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -509,14 +533,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0F6E5A1-D045-4840-AF59-CB427B762233}">
   <dimension ref="A1:M16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="27" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.28515625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="16.85546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.25" style="1" customWidth="1"/>
+    <col min="4" max="4" width="16.875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="29.25" customHeight="1">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
@@ -531,28 +555,34 @@
       </c>
       <c r="E1" s="9"/>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13">
       <c r="A2" s="6"/>
       <c r="B2"/>
       <c r="C2"/>
       <c r="D2"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="F2" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="6"/>
       <c r="B3"/>
       <c r="C3"/>
       <c r="D3"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13">
       <c r="A4" s="6"/>
       <c r="B4"/>
       <c r="C4"/>
       <c r="D4"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13">
       <c r="A5" s="6"/>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13">
       <c r="A6" s="6" t="s">
         <v>2</v>
       </c>
@@ -563,19 +593,25 @@
       <c r="D6" s="7"/>
       <c r="E6" s="7"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13">
       <c r="A7" s="6"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="F7" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7" s="12"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="12"/>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" s="6"/>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13">
       <c r="A9" s="6"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13">
       <c r="A10" s="6"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13">
       <c r="A11" s="6" t="s">
         <v>3</v>
       </c>
@@ -585,29 +621,29 @@
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
       <c r="E11" s="8"/>
-      <c r="F11" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="10"/>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13">
       <c r="A12" s="6"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="F12" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
+    </row>
+    <row r="13" spans="1:13">
       <c r="A13" s="6"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13">
       <c r="A14" s="6"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13">
       <c r="A15" s="6"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13">
       <c r="B16" s="5" t="s">
         <v>0</v>
       </c>
@@ -624,7 +660,7 @@
       <c r="M16" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="10">
     <mergeCell ref="B16:M16"/>
     <mergeCell ref="A1:A5"/>
     <mergeCell ref="A6:A10"/>
@@ -632,7 +668,9 @@
     <mergeCell ref="B6:E6"/>
     <mergeCell ref="B11:E11"/>
     <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F11:I11"/>
+    <mergeCell ref="F12:I12"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="F7:I7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
@@ -640,23 +678,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="25b9d25b-f3e3-4424-a4f0-1b70bb014b4c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E3DBFDA92D80EA48A7EED411DA26BC07" ma:contentTypeVersion="10" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="35d778446789562adff69d09f47d9821">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="25b9d25b-f3e3-4424-a4f0-1b70bb014b4c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a71633007e570e73df32b955b93894af" ns3:_="">
     <xsd:import namespace="25b9d25b-f3e3-4424-a4f0-1b70bb014b4c"/>
@@ -838,10 +859,37 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="25b9d25b-f3e3-4424-a4f0-1b70bb014b4c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5531CBBA-C22C-419D-9C9F-1BADD5578B4A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5AFFE682-A998-4D53-8B65-E4E4194E6907}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="25b9d25b-f3e3-4424-a4f0-1b70bb014b4c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -863,19 +911,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5AFFE682-A998-4D53-8B65-E4E4194E6907}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5531CBBA-C22C-419D-9C9F-1BADD5578B4A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="25b9d25b-f3e3-4424-a4f0-1b70bb014b4c"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Plannification/Planning miniProjet.xlsx
+++ b/Plannification/Planning miniProjet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\matisse.begaud\Documents\GitHub\mini_projet2\Plannification\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tristan.bonnard\Documents\GitHub\mini_projet2\Plannification\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FDB723D-C4E9-4112-993E-2B9D3F28E948}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8780E9E5-D70B-421D-9341-9D493DF0F2DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0BF01B35-82F2-4CD7-817C-7D55880151BB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{0BF01B35-82F2-4CD7-817C-7D55880151BB}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>12 heure</t>
   </si>
@@ -68,17 +68,20 @@
     <t>Cookie de connexion au chat générale</t>
   </si>
   <si>
-    <t>travailler sur le chat générale</t>
-  </si>
-  <si>
     <t>lié mail par compte</t>
+  </si>
+  <si>
+    <t>créer un README pour la procédure d'installation afin de faire fonctionner le serveur</t>
+  </si>
+  <si>
+    <t>travailler sur le chat général (style des box de texte, etc)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -99,8 +102,22 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF242424"/>
+      <name val="Aptos Narrow"/>
+      <charset val="1"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -149,6 +166,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2CEEF"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -162,7 +185,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -189,14 +212,17 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -538,6 +564,7 @@
     <col min="2" max="2" width="27" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.25" style="1" customWidth="1"/>
     <col min="4" max="4" width="16.875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="22.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="29.25" customHeight="1">
@@ -555,17 +582,19 @@
       </c>
       <c r="E1" s="9"/>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:13" ht="54" customHeight="1">
       <c r="A2" s="6"/>
       <c r="B2"/>
       <c r="C2"/>
       <c r="D2"/>
-      <c r="F2" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
+      <c r="F2" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="6"/>
@@ -595,12 +624,12 @@
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="6"/>
-      <c r="F7" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7" s="12"/>
-      <c r="H7" s="12"/>
-      <c r="I7" s="12"/>
+      <c r="F7" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="6"/>
@@ -627,12 +656,12 @@
     </row>
     <row r="12" spans="1:13">
       <c r="A12" s="6"/>
-      <c r="F12" s="11" t="s">
+      <c r="F12" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="10"/>
+      <c r="I12" s="10"/>
     </row>
     <row r="13" spans="1:13">
       <c r="A13" s="6"/>
@@ -669,8 +698,8 @@
     <mergeCell ref="B11:E11"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F12:I12"/>
-    <mergeCell ref="F2:I2"/>
     <mergeCell ref="F7:I7"/>
+    <mergeCell ref="G2:I2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
@@ -678,6 +707,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="25b9d25b-f3e3-4424-a4f0-1b70bb014b4c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E3DBFDA92D80EA48A7EED411DA26BC07" ma:contentTypeVersion="10" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="35d778446789562adff69d09f47d9821">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="25b9d25b-f3e3-4424-a4f0-1b70bb014b4c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a71633007e570e73df32b955b93894af" ns3:_="">
     <xsd:import namespace="25b9d25b-f3e3-4424-a4f0-1b70bb014b4c"/>
@@ -859,24 +905,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="25b9d25b-f3e3-4424-a4f0-1b70bb014b4c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5531CBBA-C22C-419D-9C9F-1BADD5578B4A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2E1627CE-88CC-44E6-B4B2-E6F7C128AD9F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="25b9d25b-f3e3-4424-a4f0-1b70bb014b4c"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5AFFE682-A998-4D53-8B65-E4E4194E6907}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -892,28 +945,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2E1627CE-88CC-44E6-B4B2-E6F7C128AD9F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="25b9d25b-f3e3-4424-a4f0-1b70bb014b4c"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5531CBBA-C22C-419D-9C9F-1BADD5578B4A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Plannification/Planning miniProjet.xlsx
+++ b/Plannification/Planning miniProjet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tristan.bonnard\Documents\GitHub\mini_projet2\Plannification\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8780E9E5-D70B-421D-9341-9D493DF0F2DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30D40FEC-5C08-4F49-A9EA-710512D6C405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{0BF01B35-82F2-4CD7-817C-7D55880151BB}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
   <si>
     <t>12 heure</t>
   </si>
@@ -75,6 +75,24 @@
   </si>
   <si>
     <t>travailler sur le chat général (style des box de texte, etc)</t>
+  </si>
+  <si>
+    <t>finalisation de la procédure d'intallation et de lancement de serveur</t>
+  </si>
+  <si>
+    <t>vérification du fonctionnement du projet</t>
+  </si>
+  <si>
+    <t>configuration de l'envoi d'image</t>
+  </si>
+  <si>
+    <t>création de canaux</t>
+  </si>
+  <si>
+    <t>easter egg musique soviétique</t>
+  </si>
+  <si>
+    <t>a voir</t>
   </si>
 </sst>
 </file>
@@ -117,7 +135,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -139,12 +157,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -170,6 +182,48 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFF2CEEF"/>
         <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -185,17 +239,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -212,16 +266,37 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -565,16 +640,18 @@
     <col min="3" max="3" width="18.25" style="1" customWidth="1"/>
     <col min="4" max="4" width="16.875" style="1" customWidth="1"/>
     <col min="6" max="6" width="22.125" customWidth="1"/>
+    <col min="10" max="10" width="21.5" customWidth="1"/>
+    <col min="11" max="11" width="14.375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="29.25" customHeight="1">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D1" s="9" t="s">
@@ -587,20 +664,30 @@
       <c r="B2"/>
       <c r="C2"/>
       <c r="D2"/>
-      <c r="F2" s="12" t="s">
+      <c r="F2" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="G2" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-    </row>
-    <row r="3" spans="1:13">
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+    </row>
+    <row r="3" spans="1:13" ht="42.75">
       <c r="A3" s="6"/>
       <c r="B3"/>
       <c r="C3"/>
       <c r="D3"/>
+      <c r="J3" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="K3" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="L3" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="M3" s="19"/>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="6"/>
@@ -631,8 +718,18 @@
       <c r="H7" s="11"/>
       <c r="I7" s="11"/>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:13" ht="28.5">
       <c r="A8" s="6"/>
+      <c r="J8" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="K8" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="L8" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="M8" s="18"/>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="6"/>
@@ -665,6 +762,9 @@
     </row>
     <row r="13" spans="1:13">
       <c r="A13" s="6"/>
+      <c r="J13" s="4" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="14" spans="1:13">
       <c r="A14" s="6"/>
@@ -689,7 +789,7 @@
       <c r="M16" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="12">
     <mergeCell ref="B16:M16"/>
     <mergeCell ref="A1:A5"/>
     <mergeCell ref="A6:A10"/>
@@ -700,6 +800,8 @@
     <mergeCell ref="F12:I12"/>
     <mergeCell ref="F7:I7"/>
     <mergeCell ref="G2:I2"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="L3:M3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
@@ -707,23 +809,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="25b9d25b-f3e3-4424-a4f0-1b70bb014b4c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E3DBFDA92D80EA48A7EED411DA26BC07" ma:contentTypeVersion="10" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="35d778446789562adff69d09f47d9821">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="25b9d25b-f3e3-4424-a4f0-1b70bb014b4c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a71633007e570e73df32b955b93894af" ns3:_="">
     <xsd:import namespace="25b9d25b-f3e3-4424-a4f0-1b70bb014b4c"/>
@@ -905,10 +990,37 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="25b9d25b-f3e3-4424-a4f0-1b70bb014b4c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5531CBBA-C22C-419D-9C9F-1BADD5578B4A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5AFFE682-A998-4D53-8B65-E4E4194E6907}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="25b9d25b-f3e3-4424-a4f0-1b70bb014b4c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -930,19 +1042,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5AFFE682-A998-4D53-8B65-E4E4194E6907}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5531CBBA-C22C-419D-9C9F-1BADD5578B4A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="25b9d25b-f3e3-4424-a4f0-1b70bb014b4c"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Plannification/Planning miniProjet.xlsx
+++ b/Plannification/Planning miniProjet.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tristan.bonnard\Documents\GitHub\mini_projet2\Plannification\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stfelixlasalle-my.sharepoint.com/personal/julian_chedotal_stfelixlasalle_fr/Documents/Documents/GitHub/mini_projet2/mini_projet2/Plannification/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30D40FEC-5C08-4F49-A9EA-710512D6C405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{30D40FEC-5C08-4F49-A9EA-710512D6C405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8806CD94-3391-44D6-BDE1-FBB0FDEE13A9}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{0BF01B35-82F2-4CD7-817C-7D55880151BB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0BF01B35-82F2-4CD7-817C-7D55880151BB}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>12 heure</t>
   </si>
@@ -93,13 +93,19 @@
   </si>
   <si>
     <t>a voir</t>
+  </si>
+  <si>
+    <t>Photo de profil</t>
+  </si>
+  <si>
+    <t>à voir</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -135,7 +141,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -223,6 +229,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -248,21 +260,36 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -275,29 +302,14 @@
     <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -634,54 +646,54 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0F6E5A1-D045-4840-AF59-CB427B762233}">
   <dimension ref="A1:M16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="27" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.25" style="1" customWidth="1"/>
-    <col min="4" max="4" width="16.875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="22.125" customWidth="1"/>
-    <col min="10" max="10" width="21.5" customWidth="1"/>
-    <col min="11" max="11" width="14.375" customWidth="1"/>
+    <col min="3" max="3" width="18.28515625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="16.85546875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="22.140625" customWidth="1"/>
+    <col min="10" max="10" width="21.42578125" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="29.25" customHeight="1">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="9"/>
-    </row>
-    <row r="2" spans="1:13" ht="54" customHeight="1">
-      <c r="A2" s="6"/>
+      <c r="E1" s="14"/>
+    </row>
+    <row r="2" spans="1:13" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="11"/>
       <c r="B2"/>
       <c r="C2"/>
       <c r="D2"/>
-      <c r="F2" s="14" t="s">
+      <c r="F2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="G2" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-    </row>
-    <row r="3" spans="1:13" ht="42.75">
-      <c r="A3" s="6"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+    </row>
+    <row r="3" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="A3" s="11"/>
       <c r="B3"/>
       <c r="C3"/>
       <c r="D3"/>
-      <c r="J3" s="15" t="s">
+      <c r="J3" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="K3" s="20" t="s">
+      <c r="K3" s="9" t="s">
         <v>17</v>
       </c>
       <c r="L3" s="19" t="s">
@@ -689,107 +701,112 @@
       </c>
       <c r="M3" s="19"/>
     </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="6"/>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="11"/>
       <c r="B4"/>
       <c r="C4"/>
       <c r="D4"/>
     </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="6"/>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="6" t="s">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="11"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="6"/>
-      <c r="F7" s="11" t="s">
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" s="11"/>
+      <c r="F7" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="11"/>
-    </row>
-    <row r="8" spans="1:13" ht="28.5">
-      <c r="A8" s="6"/>
-      <c r="J8" s="16" t="s">
+      <c r="G7" s="16"/>
+      <c r="H7" s="16"/>
+      <c r="I7" s="16"/>
+    </row>
+    <row r="8" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A8" s="11"/>
+      <c r="J8" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="K8" s="17" t="s">
+      <c r="K8" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="L8" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="M8" s="18"/>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="6"/>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="6"/>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="6" t="s">
+      <c r="L8" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="M8" s="20"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" s="11"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" s="11"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
     </row>
-    <row r="12" spans="1:13">
-      <c r="A12" s="6"/>
-      <c r="F12" s="10" t="s">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" s="11"/>
+      <c r="F12" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10"/>
-      <c r="I12" s="10"/>
-    </row>
-    <row r="13" spans="1:13">
-      <c r="A13" s="6"/>
-      <c r="J13" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
-      <c r="A14" s="6"/>
-    </row>
-    <row r="15" spans="1:13">
-      <c r="A15" s="6"/>
-    </row>
-    <row r="16" spans="1:13">
-      <c r="B16" s="5" t="s">
+      <c r="G12" s="15"/>
+      <c r="H12" s="15"/>
+      <c r="I12" s="15"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" s="11"/>
+      <c r="J13" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="K13" s="18"/>
+      <c r="L13" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="M13" s="20"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" s="11"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" s="11"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B16" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
-      <c r="J16" s="5"/>
-      <c r="K16" s="5"/>
-      <c r="L16" s="5"/>
-      <c r="M16" s="5"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="10"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="10"/>
+      <c r="J16" s="10"/>
+      <c r="K16" s="10"/>
+      <c r="L16" s="10"/>
+      <c r="M16" s="10"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="14">
     <mergeCell ref="B16:M16"/>
     <mergeCell ref="A1:A5"/>
     <mergeCell ref="A6:A10"/>
@@ -800,8 +817,10 @@
     <mergeCell ref="F12:I12"/>
     <mergeCell ref="F7:I7"/>
     <mergeCell ref="G2:I2"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="L13:M13"/>
     <mergeCell ref="L8:M8"/>
-    <mergeCell ref="L3:M3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
@@ -809,6 +828,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="25b9d25b-f3e3-4424-a4f0-1b70bb014b4c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E3DBFDA92D80EA48A7EED411DA26BC07" ma:contentTypeVersion="10" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="35d778446789562adff69d09f47d9821">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="25b9d25b-f3e3-4424-a4f0-1b70bb014b4c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a71633007e570e73df32b955b93894af" ns3:_="">
     <xsd:import namespace="25b9d25b-f3e3-4424-a4f0-1b70bb014b4c"/>
@@ -990,37 +1026,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="25b9d25b-f3e3-4424-a4f0-1b70bb014b4c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5AFFE682-A998-4D53-8B65-E4E4194E6907}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5531CBBA-C22C-419D-9C9F-1BADD5578B4A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="25b9d25b-f3e3-4424-a4f0-1b70bb014b4c"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1042,9 +1051,19 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5531CBBA-C22C-419D-9C9F-1BADD5578B4A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5AFFE682-A998-4D53-8B65-E4E4194E6907}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="25b9d25b-f3e3-4424-a4f0-1b70bb014b4c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Plannification/Planning miniProjet.xlsx
+++ b/Plannification/Planning miniProjet.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stfelixlasalle-my.sharepoint.com/personal/julian_chedotal_stfelixlasalle_fr/Documents/Documents/GitHub/mini_projet2/mini_projet2/Plannification/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tristan.bonnard\Documents\GitHub\mini_projet2\Plannification\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{30D40FEC-5C08-4F49-A9EA-710512D6C405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8806CD94-3391-44D6-BDE1-FBB0FDEE13A9}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64E5C9BF-7CDE-4469-85B8-385B5631410F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0BF01B35-82F2-4CD7-817C-7D55880151BB}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="18900" windowHeight="10965" xr2:uid="{0BF01B35-82F2-4CD7-817C-7D55880151BB}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -92,20 +92,20 @@
     <t>easter egg musique soviétique</t>
   </si>
   <si>
-    <t>a voir</t>
-  </si>
-  <si>
     <t>Photo de profil</t>
   </si>
   <si>
     <t>à voir</t>
+  </si>
+  <si>
+    <t>ajout du logo en favicon sur l'onglet de chaque HTML du site et retrait de la mascotte du header de menu_principal.html</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -646,17 +646,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0F6E5A1-D045-4840-AF59-CB427B762233}">
   <dimension ref="A1:M16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="27" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.28515625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="16.85546875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="22.140625" customWidth="1"/>
-    <col min="10" max="10" width="21.42578125" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" customWidth="1"/>
+    <col min="3" max="3" width="18.25" style="1" customWidth="1"/>
+    <col min="4" max="4" width="16.875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="22.125" customWidth="1"/>
+    <col min="10" max="10" width="21.375" customWidth="1"/>
+    <col min="11" max="11" width="14.375" customWidth="1"/>
+    <col min="13" max="13" width="17.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="29.25" customHeight="1">
       <c r="A1" s="11" t="s">
         <v>1</v>
       </c>
@@ -671,7 +672,7 @@
       </c>
       <c r="E1" s="14"/>
     </row>
-    <row r="2" spans="1:13" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" ht="54" customHeight="1">
       <c r="A2" s="11"/>
       <c r="B2"/>
       <c r="C2"/>
@@ -685,7 +686,7 @@
       <c r="H2" s="17"/>
       <c r="I2" s="17"/>
     </row>
-    <row r="3" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" ht="55.5" customHeight="1">
       <c r="A3" s="11"/>
       <c r="B3"/>
       <c r="C3"/>
@@ -697,20 +698,20 @@
         <v>17</v>
       </c>
       <c r="L3" s="19" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M3" s="19"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13">
       <c r="A4" s="11"/>
       <c r="B4"/>
       <c r="C4"/>
       <c r="D4"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13">
       <c r="A5" s="11"/>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13">
       <c r="A6" s="11" t="s">
         <v>2</v>
       </c>
@@ -721,7 +722,7 @@
       <c r="D6" s="12"/>
       <c r="E6" s="12"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13">
       <c r="A7" s="11"/>
       <c r="F7" s="16" t="s">
         <v>10</v>
@@ -730,7 +731,7 @@
       <c r="H7" s="16"/>
       <c r="I7" s="16"/>
     </row>
-    <row r="8" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" ht="28.5">
       <c r="A8" s="11"/>
       <c r="J8" s="7" t="s">
         <v>14</v>
@@ -739,17 +740,17 @@
         <v>15</v>
       </c>
       <c r="L8" s="20" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M8" s="20"/>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13">
       <c r="A9" s="11"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13">
       <c r="A10" s="11"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13">
       <c r="A11" s="11" t="s">
         <v>3</v>
       </c>
@@ -763,7 +764,7 @@
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13">
       <c r="A12" s="11"/>
       <c r="F12" s="15" t="s">
         <v>9</v>
@@ -772,24 +773,24 @@
       <c r="H12" s="15"/>
       <c r="I12" s="15"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13">
       <c r="A13" s="11"/>
       <c r="J13" s="18" t="s">
         <v>16</v>
       </c>
       <c r="K13" s="18"/>
       <c r="L13" s="20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M13" s="20"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13">
       <c r="A14" s="11"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13">
       <c r="A15" s="11"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13">
       <c r="B16" s="10" t="s">
         <v>0</v>
       </c>
@@ -828,23 +829,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="25b9d25b-f3e3-4424-a4f0-1b70bb014b4c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E3DBFDA92D80EA48A7EED411DA26BC07" ma:contentTypeVersion="10" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="35d778446789562adff69d09f47d9821">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="25b9d25b-f3e3-4424-a4f0-1b70bb014b4c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a71633007e570e73df32b955b93894af" ns3:_="">
     <xsd:import namespace="25b9d25b-f3e3-4424-a4f0-1b70bb014b4c"/>
@@ -1026,10 +1010,37 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="25b9d25b-f3e3-4424-a4f0-1b70bb014b4c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5531CBBA-C22C-419D-9C9F-1BADD5578B4A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5AFFE682-A998-4D53-8B65-E4E4194E6907}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="25b9d25b-f3e3-4424-a4f0-1b70bb014b4c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1051,19 +1062,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5AFFE682-A998-4D53-8B65-E4E4194E6907}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5531CBBA-C22C-419D-9C9F-1BADD5578B4A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="25b9d25b-f3e3-4424-a4f0-1b70bb014b4c"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Plannification/Planning miniProjet.xlsx
+++ b/Plannification/Planning miniProjet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tristan.bonnard\Documents\GitHub\mini_projet2\Plannification\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64E5C9BF-7CDE-4469-85B8-385B5631410F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CDEB757-C11F-4FE5-B15D-DFB3CD50432B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="18900" windowHeight="10965" xr2:uid="{0BF01B35-82F2-4CD7-817C-7D55880151BB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0BF01B35-82F2-4CD7-817C-7D55880151BB}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>12 heure</t>
   </si>
@@ -95,17 +95,26 @@
     <t>Photo de profil</t>
   </si>
   <si>
-    <t>à voir</t>
-  </si>
-  <si>
     <t>ajout du logo en favicon sur l'onglet de chaque HTML du site et retrait de la mascotte du header de menu_principal.html</t>
+  </si>
+  <si>
+    <t>renommage de fonctions et constantes et ajout de commentaires pour la compréhension du code</t>
+  </si>
+  <si>
+    <t>ajout de scénarios pour la fiche recette</t>
+  </si>
+  <si>
+    <t>affichage de l'heure des messages et création de groupe</t>
+  </si>
+  <si>
+    <t>création de groupes</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -141,7 +150,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -235,6 +244,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0099FF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -251,7 +266,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -310,6 +325,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -317,6 +344,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF0099FF"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -645,19 +677,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0F6E5A1-D045-4840-AF59-CB427B762233}">
-  <dimension ref="A1:M16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
+  <dimension ref="A1:O16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="27" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.25" style="1" customWidth="1"/>
-    <col min="4" max="4" width="16.875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="22.125" customWidth="1"/>
-    <col min="10" max="10" width="21.375" customWidth="1"/>
-    <col min="11" max="11" width="14.375" customWidth="1"/>
-    <col min="13" max="13" width="17.125" customWidth="1"/>
+    <col min="3" max="3" width="18.28515625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="16.85546875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="22.140625" customWidth="1"/>
+    <col min="10" max="10" width="21.42578125" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" customWidth="1"/>
+    <col min="13" max="13" width="17.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="29.25" customHeight="1">
+    <row r="1" spans="1:15" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>1</v>
       </c>
@@ -672,7 +704,7 @@
       </c>
       <c r="E1" s="14"/>
     </row>
-    <row r="2" spans="1:13" ht="54" customHeight="1">
+    <row r="2" spans="1:15" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11"/>
       <c r="B2"/>
       <c r="C2"/>
@@ -686,7 +718,7 @@
       <c r="H2" s="17"/>
       <c r="I2" s="17"/>
     </row>
-    <row r="3" spans="1:13" ht="55.5" customHeight="1">
+    <row r="3" spans="1:15" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11"/>
       <c r="B3"/>
       <c r="C3"/>
@@ -698,20 +730,24 @@
         <v>17</v>
       </c>
       <c r="L3" s="19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M3" s="19"/>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11"/>
       <c r="B4"/>
       <c r="C4"/>
       <c r="D4"/>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="11"/>
-    </row>
-    <row r="6" spans="1:13">
+      <c r="N4" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="O4" s="21"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" s="22"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>2</v>
       </c>
@@ -722,7 +758,7 @@
       <c r="D6" s="12"/>
       <c r="E6" s="12"/>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="11"/>
       <c r="F7" s="16" t="s">
         <v>10</v>
@@ -731,7 +767,7 @@
       <c r="H7" s="16"/>
       <c r="I7" s="16"/>
     </row>
-    <row r="8" spans="1:13" ht="28.5">
+    <row r="8" spans="1:15" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="11"/>
       <c r="J8" s="7" t="s">
         <v>14</v>
@@ -744,13 +780,17 @@
       </c>
       <c r="M8" s="20"/>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:15" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11"/>
-    </row>
-    <row r="10" spans="1:13">
+      <c r="N9" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="O9" s="23"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="11"/>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>3</v>
       </c>
@@ -764,7 +804,7 @@
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="11"/>
       <c r="F12" s="15" t="s">
         <v>9</v>
@@ -773,24 +813,28 @@
       <c r="H12" s="15"/>
       <c r="I12" s="15"/>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="11"/>
       <c r="J13" s="18" t="s">
         <v>16</v>
       </c>
       <c r="K13" s="18"/>
       <c r="L13" s="20" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="M13" s="20"/>
     </row>
-    <row r="14" spans="1:13">
+    <row r="14" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11"/>
-    </row>
-    <row r="15" spans="1:13">
+      <c r="N14" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="O14" s="24"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="11"/>
     </row>
-    <row r="16" spans="1:13">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B16" s="10" t="s">
         <v>0</v>
       </c>
@@ -807,9 +851,12 @@
       <c r="M16" s="10"/>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="17">
+    <mergeCell ref="N4:O4"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="A1:A4"/>
+    <mergeCell ref="N14:O14"/>
     <mergeCell ref="B16:M16"/>
-    <mergeCell ref="A1:A5"/>
     <mergeCell ref="A6:A10"/>
     <mergeCell ref="A11:A15"/>
     <mergeCell ref="B6:E6"/>
@@ -829,6 +876,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="25b9d25b-f3e3-4424-a4f0-1b70bb014b4c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E3DBFDA92D80EA48A7EED411DA26BC07" ma:contentTypeVersion="10" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="35d778446789562adff69d09f47d9821">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="25b9d25b-f3e3-4424-a4f0-1b70bb014b4c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a71633007e570e73df32b955b93894af" ns3:_="">
     <xsd:import namespace="25b9d25b-f3e3-4424-a4f0-1b70bb014b4c"/>
@@ -1010,37 +1074,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="25b9d25b-f3e3-4424-a4f0-1b70bb014b4c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5AFFE682-A998-4D53-8B65-E4E4194E6907}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5531CBBA-C22C-419D-9C9F-1BADD5578B4A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="25b9d25b-f3e3-4424-a4f0-1b70bb014b4c"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1062,9 +1099,19 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5531CBBA-C22C-419D-9C9F-1BADD5578B4A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5AFFE682-A998-4D53-8B65-E4E4194E6907}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="25b9d25b-f3e3-4424-a4f0-1b70bb014b4c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>